--- a/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-25).xlsx
+++ b/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-25).xlsx
@@ -935,31 +935,31 @@
     <t>214</t>
   </si>
   <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>R$ 9.444,00</t>
-  </si>
-  <si>
-    <t>99.5</t>
-  </si>
-  <si>
-    <t>66.6</t>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 9.405,97</t>
+  </si>
+  <si>
+    <t>99.1</t>
+  </si>
+  <si>
+    <t>66.3</t>
   </si>
   <si>
     <t>6.32</t>
   </si>
   <si>
-    <t>20.9</t>
+    <t>21.0</t>
   </si>
   <si>
     <t>7.7</t>
   </si>
   <si>
-    <t>6.0</t>
-  </si>
-  <si>
-    <t>32.1%</t>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>32.3%</t>
   </si>
   <si>
     <t>17.9%</t>
@@ -4912,7 +4912,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>51</v>
@@ -4942,14 +4942,26 @@
         <v>58</v>
       </c>
       <c r="L24" s="4"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="6"/>
+      <c r="M24" s="5">
+        <v>10360.030000000001</v>
+      </c>
+      <c r="N24" s="6">
+        <v>116</v>
+      </c>
       <c r="O24" s="6"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="8"/>
+      <c r="P24" s="7">
+        <v>5.1401176991150441</v>
+      </c>
+      <c r="Q24" s="8">
+        <v>20.652355434782606</v>
+      </c>
+      <c r="R24" s="8">
+        <v>8.5481880434782607</v>
+      </c>
       <c r="S24" s="8"/>
-      <c r="T24" s="9"/>
+      <c r="T24" s="9">
+        <v>0.28260869565217389</v>
+      </c>
       <c r="U24" s="9"/>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -10785,7 +10797,7 @@
         <v>19632</v>
       </c>
       <c r="B63" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C63" s="4">
         <v>51</v>
@@ -10815,10 +10827,16 @@
         <v>58</v>
       </c>
       <c r="L63" s="4"/>
-      <c r="M63" s="5"/>
-      <c r="N63" s="6"/>
+      <c r="M63" s="5">
+        <v>0</v>
+      </c>
+      <c r="N63" s="6">
+        <v>101</v>
+      </c>
       <c r="O63" s="6"/>
-      <c r="P63" s="7"/>
+      <c r="P63" s="7">
+        <v>0.19288058252427187</v>
+      </c>
       <c r="Q63" s="8"/>
       <c r="R63" s="8"/>
       <c r="S63" s="8"/>
@@ -14611,7 +14629,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14639,14 +14657,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>8514.7600000000002</v>
+      </c>
+      <c r="N89" s="6">
+        <v>77</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>12.15458375</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>32.428493548387095</v>
+      </c>
+      <c r="R89" s="8">
+        <v>9.4747322580645168</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
@@ -32107,7 +32137,7 @@
         <v>19962</v>
       </c>
       <c r="B207" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C207" s="4">
         <v>51</v>
@@ -32137,35 +32167,93 @@
         <v>58</v>
       </c>
       <c r="L207" s="4"/>
-      <c r="M207" s="5"/>
-      <c r="N207" s="6"/>
-      <c r="O207" s="6"/>
-      <c r="P207" s="7"/>
-      <c r="Q207" s="8"/>
-      <c r="R207" s="8"/>
-      <c r="S207" s="8"/>
-      <c r="T207" s="9"/>
-      <c r="U207" s="9"/>
-      <c r="V207" s="9"/>
-      <c r="W207" s="9"/>
-      <c r="X207" s="9"/>
-      <c r="Y207" s="9"/>
-      <c r="Z207" s="9"/>
-      <c r="AA207" s="9"/>
-      <c r="AB207" s="9"/>
-      <c r="AC207" s="9"/>
-      <c r="AD207" s="6"/>
-      <c r="AE207" s="6"/>
-      <c r="AF207" s="6"/>
-      <c r="AG207" s="6"/>
-      <c r="AH207" s="6"/>
-      <c r="AI207" s="6"/>
-      <c r="AJ207" s="6"/>
-      <c r="AK207" s="6"/>
-      <c r="AL207" s="6"/>
-      <c r="AM207" s="6"/>
-      <c r="AN207" s="9"/>
-      <c r="AO207" s="6"/>
+      <c r="M207" s="5">
+        <v>2460.1199999999999</v>
+      </c>
+      <c r="N207" s="6">
+        <v>27</v>
+      </c>
+      <c r="O207" s="6">
+        <v>18</v>
+      </c>
+      <c r="P207" s="7">
+        <v>7.8086407407407412</v>
+      </c>
+      <c r="Q207" s="8">
+        <v>21.717594444444444</v>
+      </c>
+      <c r="R207" s="8">
+        <v>6.9675944444444449</v>
+      </c>
+      <c r="S207" s="8">
+        <v>7</v>
+      </c>
+      <c r="T207" s="9">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="U207" s="9">
+        <v>0</v>
+      </c>
+      <c r="V207" s="9">
+        <v>0</v>
+      </c>
+      <c r="W207" s="9">
+        <v>0</v>
+      </c>
+      <c r="X207" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y207" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO207" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP207" s="4">
         <v>58</v>
       </c>
